--- a/artfynd/A 32402-2026 artfynd.xlsx
+++ b/artfynd/A 32402-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136145914</v>
       </c>
       <c r="B3" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145915</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145923</v>
       </c>
       <c r="B5" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145925</v>
       </c>
       <c r="B6" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32402-2026 artfynd.xlsx
+++ b/artfynd/A 32402-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136145914</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145915</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145923</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145925</v>
       </c>
       <c r="B6" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32402-2026 artfynd.xlsx
+++ b/artfynd/A 32402-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136145921</v>
       </c>
       <c r="B2" t="n">
-        <v>79569</v>
+        <v>79571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136145914</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136145915</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136145923</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136145925</v>
       </c>
       <c r="B6" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136145918</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136145926</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>136145917</v>
       </c>
       <c r="B9" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136145910</v>
       </c>
       <c r="B10" t="n">
-        <v>58870</v>
+        <v>58872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>136145911</v>
       </c>
       <c r="B11" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
